--- a/data_input/source_data/Program.xlsx
+++ b/data_input/source_data/Program.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="5">
   <si>
     <t>serialno</t>
   </si>
@@ -1275,43 +1275,43 @@
       <c r="B17" s="8">
         <v>25752</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="7">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0</v>
-      </c>
-      <c r="F17" s="7">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7">
-        <v>0</v>
-      </c>
-      <c r="H17" s="7">
-        <v>59</v>
-      </c>
-      <c r="I17" s="7">
-        <v>59</v>
-      </c>
-      <c r="J17" s="7">
-        <v>59</v>
-      </c>
-      <c r="K17" s="7">
-        <v>59</v>
-      </c>
-      <c r="L17" s="7">
-        <v>59</v>
-      </c>
-      <c r="M17" s="7">
-        <v>59</v>
-      </c>
-      <c r="N17" s="7">
-        <v>0</v>
-      </c>
-      <c r="O17" s="7">
+      <c r="C17" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>59</v>
+      </c>
+      <c r="I17" s="8">
+        <v>59</v>
+      </c>
+      <c r="J17" s="8">
+        <v>59</v>
+      </c>
+      <c r="K17" s="8">
+        <v>59</v>
+      </c>
+      <c r="L17" s="8">
+        <v>59</v>
+      </c>
+      <c r="M17" s="8">
+        <v>59</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+      <c r="O17" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1320,44 +1320,269 @@
       <c r="B18" s="8">
         <v>25479</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="7">
-        <v>0</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0</v>
-      </c>
-      <c r="F18" s="7">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7">
-        <v>59</v>
-      </c>
-      <c r="I18" s="7">
-        <v>59</v>
-      </c>
-      <c r="J18" s="7">
-        <v>59</v>
-      </c>
-      <c r="K18" s="7">
-        <v>59</v>
-      </c>
-      <c r="L18" s="7">
-        <v>59</v>
-      </c>
-      <c r="M18" s="7">
-        <v>59</v>
-      </c>
-      <c r="N18" s="7">
-        <v>0</v>
-      </c>
-      <c r="O18" s="7">
-        <v>0</v>
+      <c r="C18" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8">
+        <v>59</v>
+      </c>
+      <c r="I18" s="8">
+        <v>59</v>
+      </c>
+      <c r="J18" s="8">
+        <v>59</v>
+      </c>
+      <c r="K18" s="8">
+        <v>59</v>
+      </c>
+      <c r="L18" s="8">
+        <v>59</v>
+      </c>
+      <c r="M18" s="8">
+        <v>59</v>
+      </c>
+      <c r="N18" s="8">
+        <v>0</v>
+      </c>
+      <c r="O18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8">
+        <v>24103</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="8">
+        <v>2</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2</v>
+      </c>
+      <c r="F19" s="8">
+        <v>2</v>
+      </c>
+      <c r="G19" s="8">
+        <v>2</v>
+      </c>
+      <c r="H19" s="8">
+        <v>2</v>
+      </c>
+      <c r="I19" s="8">
+        <v>2</v>
+      </c>
+      <c r="J19" s="8">
+        <v>2</v>
+      </c>
+      <c r="K19" s="8">
+        <v>2</v>
+      </c>
+      <c r="L19" s="8">
+        <v>2</v>
+      </c>
+      <c r="M19" s="8">
+        <v>2</v>
+      </c>
+      <c r="N19" s="8">
+        <v>2</v>
+      </c>
+      <c r="O19" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8">
+        <v>25159</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="8">
+        <v>2</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2</v>
+      </c>
+      <c r="F20" s="8">
+        <v>2</v>
+      </c>
+      <c r="G20" s="8">
+        <v>2</v>
+      </c>
+      <c r="H20" s="8">
+        <v>2</v>
+      </c>
+      <c r="I20" s="8">
+        <v>2</v>
+      </c>
+      <c r="J20" s="8">
+        <v>2</v>
+      </c>
+      <c r="K20" s="8">
+        <v>2</v>
+      </c>
+      <c r="L20" s="8">
+        <v>2</v>
+      </c>
+      <c r="M20" s="8">
+        <v>2</v>
+      </c>
+      <c r="N20" s="8">
+        <v>2</v>
+      </c>
+      <c r="O20" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8">
+        <v>24287</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="8">
+        <v>2</v>
+      </c>
+      <c r="E21" s="8">
+        <v>2</v>
+      </c>
+      <c r="F21" s="8">
+        <v>2</v>
+      </c>
+      <c r="G21" s="8">
+        <v>2</v>
+      </c>
+      <c r="H21" s="8">
+        <v>2</v>
+      </c>
+      <c r="I21" s="8">
+        <v>2</v>
+      </c>
+      <c r="J21" s="8">
+        <v>2</v>
+      </c>
+      <c r="K21" s="8">
+        <v>2</v>
+      </c>
+      <c r="L21" s="8">
+        <v>2</v>
+      </c>
+      <c r="M21" s="8">
+        <v>2</v>
+      </c>
+      <c r="N21" s="8">
+        <v>2</v>
+      </c>
+      <c r="O21" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8">
+        <v>22890</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="8">
+        <v>2</v>
+      </c>
+      <c r="E22" s="8">
+        <v>2</v>
+      </c>
+      <c r="F22" s="8">
+        <v>2</v>
+      </c>
+      <c r="G22" s="8">
+        <v>2</v>
+      </c>
+      <c r="H22" s="8">
+        <v>2</v>
+      </c>
+      <c r="I22" s="8">
+        <v>2</v>
+      </c>
+      <c r="J22" s="8">
+        <v>2</v>
+      </c>
+      <c r="K22" s="8">
+        <v>2</v>
+      </c>
+      <c r="L22" s="8">
+        <v>2</v>
+      </c>
+      <c r="M22" s="8">
+        <v>2</v>
+      </c>
+      <c r="N22" s="8">
+        <v>2</v>
+      </c>
+      <c r="O22" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8">
+        <v>24488</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="8">
+        <v>2</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2</v>
+      </c>
+      <c r="F23" s="8">
+        <v>2</v>
+      </c>
+      <c r="G23" s="8">
+        <v>2</v>
+      </c>
+      <c r="H23" s="8">
+        <v>2</v>
+      </c>
+      <c r="I23" s="8">
+        <v>2</v>
+      </c>
+      <c r="J23" s="8">
+        <v>2</v>
+      </c>
+      <c r="K23" s="8">
+        <v>2</v>
+      </c>
+      <c r="L23" s="8">
+        <v>2</v>
+      </c>
+      <c r="M23" s="8">
+        <v>2</v>
+      </c>
+      <c r="N23" s="8">
+        <v>2</v>
+      </c>
+      <c r="O23" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="303" spans="5:5" x14ac:dyDescent="0.35"/>
